--- a/testdata/logindata.xlsx
+++ b/testdata/logindata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shashank Mundaye\IdeaProjects\SDET\automation-demo\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA653401-727E-4658-AF37-8228FB5EED79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3BF741-E1F1-4C04-8575-B606574F146F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5162C306-CD0E-4DD1-B50E-88C57AFB2020}"/>
+    <workbookView xWindow="4800" yWindow="3110" windowWidth="14400" windowHeight="8170" xr2:uid="{5162C306-CD0E-4DD1-B50E-88C57AFB2020}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -62,25 +62,17 @@
     <t>dummy</t>
   </si>
   <si>
-    <t>dummy@12</t>
+    <t>dummy123</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -103,16 +95,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -474,7 +463,7 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
@@ -482,9 +471,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{25F41E68-AE13-4D9C-B2CF-2A56FA478A8B}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>